--- a/Assets/Configs/SpawnRoots.xlsx
+++ b/Assets/Configs/SpawnRoots.xlsx
@@ -1,33 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\minigame\Assets\Configs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAD710B8-F208-4C60-A7BA-DDD99F6E8A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="19200" windowHeight="9970"/>
+    <workbookView windowWidth="25600" windowHeight="10600"/>
   </bookViews>
   <sheets>
     <sheet name="SpawnRoots" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>RootID</t>
+  </si>
+  <si>
+    <t>RoundID</t>
   </si>
   <si>
     <t>EnemyID</t>
@@ -35,25 +40,48 @@
   <si>
     <t>SpawnGap</t>
   </si>
+  <si>
+    <t>EnemyNum</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -61,16 +89,22 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="等线 Light"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -79,7 +113,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -88,31 +121,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -120,7 +128,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -129,7 +136,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -138,15 +144,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -155,24 +152,13 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -181,7 +167,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -189,14 +195,6 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -210,175 +208,188 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -388,6 +399,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -413,7 +439,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -448,15 +474,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -472,17 +489,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -498,131 +509,152 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -631,58 +663,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -731,7 +766,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -764,26 +799,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -816,23 +834,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -974,21 +975,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="5" width="12.8333333333333" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -998,8 +997,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>101</v>
       </c>
@@ -1007,11 +1012,510 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0.6</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>0.6</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>101</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0.6</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>101</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0.6</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>101</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0.6</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>101</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0.6</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>101</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0.6</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>101</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0.6</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>101</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>0.6</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>101</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>0.6</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>101</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>0.6</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>102</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0.6</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>102</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0.6</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>102</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>0.6</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>102</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0.6</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>102</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0.6</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>102</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0.6</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>102</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>0.6</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>102</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>0.6</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>102</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>0.6</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>102</v>
+      </c>
+      <c r="B21">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>0.6</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>103</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>0.6</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>103</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>0.6</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>103</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>0.6</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>103</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>0.6</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>103</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>0.6</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>103</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>0.6</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>103</v>
+      </c>
+      <c r="B28">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>0.6</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>103</v>
+      </c>
+      <c r="B29">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>0.6</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>103</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>0.6</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>103</v>
+      </c>
+      <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>0.6</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Configs/SpawnRoots.xlsx
+++ b/Assets/Configs/SpawnRoots.xlsx
@@ -1,28 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41055C46-7054-4F42-880E-B855FC70D8D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10600"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpawnRoots" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -47,14 +40,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="19">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,337 +50,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线 Light"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -401,260 +73,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -663,61 +84,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -975,19 +352,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="12.8333333333333" customWidth="1"/>
+    <col min="1" max="5" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1004,7 +381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101</v>
       </c>
@@ -1012,7 +389,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="D2">
         <v>0.6</v>
@@ -1021,7 +398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>101</v>
       </c>
@@ -1029,7 +406,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="D3">
         <v>0.6</v>
@@ -1038,7 +415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>101</v>
       </c>
@@ -1046,7 +423,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="D4">
         <v>0.6</v>
@@ -1055,7 +432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>101</v>
       </c>
@@ -1063,7 +440,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="D5">
         <v>0.6</v>
@@ -1072,7 +449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>101</v>
       </c>
@@ -1080,7 +457,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="D6">
         <v>0.6</v>
@@ -1089,7 +466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>101</v>
       </c>
@@ -1097,7 +474,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="D7">
         <v>0.6</v>
@@ -1106,7 +483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>101</v>
       </c>
@@ -1114,7 +491,7 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="D8">
         <v>0.6</v>
@@ -1123,7 +500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>101</v>
       </c>
@@ -1131,7 +508,7 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="D9">
         <v>0.6</v>
@@ -1140,7 +517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>101</v>
       </c>
@@ -1148,7 +525,7 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="D10">
         <v>0.6</v>
@@ -1157,7 +534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>101</v>
       </c>
@@ -1165,7 +542,7 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="D11">
         <v>0.6</v>
@@ -1174,7 +551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>102</v>
       </c>
@@ -1182,7 +559,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D12">
         <v>0.6</v>
@@ -1191,7 +568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>102</v>
       </c>
@@ -1199,7 +576,7 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D13">
         <v>0.6</v>
@@ -1208,7 +585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>102</v>
       </c>
@@ -1216,7 +593,7 @@
         <v>3</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D14">
         <v>0.6</v>
@@ -1225,7 +602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>102</v>
       </c>
@@ -1233,7 +610,7 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D15">
         <v>0.6</v>
@@ -1242,7 +619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>102</v>
       </c>
@@ -1250,7 +627,7 @@
         <v>5</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D16">
         <v>0.6</v>
@@ -1259,7 +636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>102</v>
       </c>
@@ -1267,7 +644,7 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D17">
         <v>0.6</v>
@@ -1276,7 +653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>102</v>
       </c>
@@ -1284,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D18">
         <v>0.6</v>
@@ -1293,7 +670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>102</v>
       </c>
@@ -1301,7 +678,7 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D19">
         <v>0.6</v>
@@ -1310,7 +687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>102</v>
       </c>
@@ -1318,7 +695,7 @@
         <v>9</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D20">
         <v>0.6</v>
@@ -1327,7 +704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>102</v>
       </c>
@@ -1335,7 +712,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D21">
         <v>0.6</v>
@@ -1344,7 +721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>103</v>
       </c>
@@ -1352,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="D22">
         <v>0.6</v>
@@ -1361,7 +738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>103</v>
       </c>
@@ -1369,7 +746,7 @@
         <v>2</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="D23">
         <v>0.6</v>
@@ -1378,7 +755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>103</v>
       </c>
@@ -1386,7 +763,7 @@
         <v>3</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="D24">
         <v>0.6</v>
@@ -1395,7 +772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>103</v>
       </c>
@@ -1403,7 +780,7 @@
         <v>4</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="D25">
         <v>0.6</v>
@@ -1412,7 +789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>103</v>
       </c>
@@ -1420,7 +797,7 @@
         <v>5</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="D26">
         <v>0.6</v>
@@ -1429,7 +806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>103</v>
       </c>
@@ -1437,7 +814,7 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="D27">
         <v>0.6</v>
@@ -1446,7 +823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>103</v>
       </c>
@@ -1454,7 +831,7 @@
         <v>7</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="D28">
         <v>0.6</v>
@@ -1463,7 +840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>103</v>
       </c>
@@ -1471,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="D29">
         <v>0.6</v>
@@ -1480,7 +857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>103</v>
       </c>
@@ -1488,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="D30">
         <v>0.6</v>
@@ -1497,7 +874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>103</v>
       </c>
@@ -1505,7 +882,7 @@
         <v>10</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="D31">
         <v>0.6</v>
@@ -1515,7 +892,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Configs/SpawnRoots.xlsx
+++ b/Assets/Configs/SpawnRoots.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41055C46-7054-4F42-880E-B855FC70D8D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA25F50-99B0-433E-AAE4-A6D9AC548581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpawnRoots" sheetId="1" r:id="rId1"/>
@@ -41,17 +41,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -359,12 +359,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="5" width="12.83203125" customWidth="1"/>
+    <col min="1" max="5" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -381,7 +381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>101</v>
       </c>
@@ -395,10 +395,10 @@
         <v>0.6</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>101</v>
       </c>
@@ -412,10 +412,10 @@
         <v>0.6</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>101</v>
       </c>
@@ -426,13 +426,13 @@
         <v>1001</v>
       </c>
       <c r="D4">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>101</v>
       </c>
@@ -443,13 +443,13 @@
         <v>1001</v>
       </c>
       <c r="D5">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>101</v>
       </c>
@@ -460,13 +460,13 @@
         <v>1001</v>
       </c>
       <c r="D6">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>101</v>
       </c>
@@ -477,13 +477,13 @@
         <v>1001</v>
       </c>
       <c r="D7">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>101</v>
       </c>
@@ -494,13 +494,13 @@
         <v>1001</v>
       </c>
       <c r="D8">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>101</v>
       </c>
@@ -511,13 +511,13 @@
         <v>1001</v>
       </c>
       <c r="D9">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>101</v>
       </c>
@@ -528,13 +528,13 @@
         <v>1001</v>
       </c>
       <c r="D10">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>101</v>
       </c>
@@ -545,13 +545,13 @@
         <v>1001</v>
       </c>
       <c r="D11">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>102</v>
       </c>
@@ -568,7 +568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>102</v>
       </c>
@@ -585,7 +585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>102</v>
       </c>
@@ -602,7 +602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>102</v>
       </c>
@@ -619,7 +619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>102</v>
       </c>
@@ -636,7 +636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>102</v>
       </c>
@@ -653,7 +653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>102</v>
       </c>
@@ -670,7 +670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>102</v>
       </c>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>102</v>
       </c>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>102</v>
       </c>
@@ -721,7 +721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>103</v>
       </c>
@@ -738,7 +738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>103</v>
       </c>
@@ -755,7 +755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>103</v>
       </c>
@@ -772,7 +772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>103</v>
       </c>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>103</v>
       </c>
@@ -806,7 +806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>103</v>
       </c>
@@ -823,7 +823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>103</v>
       </c>
@@ -840,7 +840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>103</v>
       </c>
@@ -857,7 +857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>103</v>
       </c>
@@ -874,7 +874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>103</v>
       </c>

--- a/Assets/Configs/SpawnRoots.xlsx
+++ b/Assets/Configs/SpawnRoots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA25F50-99B0-433E-AAE4-A6D9AC548581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76DEA35-1678-4D56-8359-6F1751128473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -395,7 +395,7 @@
         <v>0.6</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -412,7 +412,7 @@
         <v>0.6</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -429,7 +429,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -446,7 +446,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -463,7 +463,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -480,7 +480,7 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -497,7 +497,7 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -531,7 +531,7 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -548,7 +548,7 @@
         <v>3</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -565,7 +565,7 @@
         <v>0.6</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -582,7 +582,7 @@
         <v>0.6</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -596,7 +596,7 @@
         <v>1002</v>
       </c>
       <c r="D14">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -613,7 +613,7 @@
         <v>1002</v>
       </c>
       <c r="D15">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -630,7 +630,7 @@
         <v>1002</v>
       </c>
       <c r="D16">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -647,10 +647,10 @@
         <v>1002</v>
       </c>
       <c r="D17">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -664,10 +664,10 @@
         <v>1002</v>
       </c>
       <c r="D18">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -681,10 +681,10 @@
         <v>1002</v>
       </c>
       <c r="D19">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -698,10 +698,10 @@
         <v>1002</v>
       </c>
       <c r="D20">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -715,10 +715,10 @@
         <v>1002</v>
       </c>
       <c r="D21">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -735,7 +735,7 @@
         <v>0.6</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -752,7 +752,7 @@
         <v>0.6</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -766,10 +766,10 @@
         <v>1003</v>
       </c>
       <c r="D24">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -783,10 +783,10 @@
         <v>1003</v>
       </c>
       <c r="D25">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -800,10 +800,10 @@
         <v>1003</v>
       </c>
       <c r="D26">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -817,7 +817,7 @@
         <v>1003</v>
       </c>
       <c r="D27">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -834,7 +834,7 @@
         <v>1003</v>
       </c>
       <c r="D28">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -851,7 +851,7 @@
         <v>1003</v>
       </c>
       <c r="D29">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -868,10 +868,10 @@
         <v>1003</v>
       </c>
       <c r="D30">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -885,10 +885,10 @@
         <v>1003</v>
       </c>
       <c r="D31">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/SpawnRoots.xlsx
+++ b/Assets/Configs/SpawnRoots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76DEA35-1678-4D56-8359-6F1751128473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24DD1449-F171-4514-B41B-ABF514CB3D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -395,7 +395,7 @@
         <v>0.6</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -412,7 +412,7 @@
         <v>0.6</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -735,7 +735,7 @@
         <v>0.6</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -752,7 +752,7 @@
         <v>0.6</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">

--- a/Assets/Configs/SpawnRoots.xlsx
+++ b/Assets/Configs/SpawnRoots.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24DD1449-F171-4514-B41B-ABF514CB3D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506FDCCF-35F6-4CB5-AB24-90F1AFC6C7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -480,7 +480,7 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -497,7 +497,7 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -531,7 +531,7 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -548,7 +548,7 @@
         <v>3</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -698,7 +698,7 @@
         <v>1002</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20">
         <v>4</v>
@@ -718,7 +718,7 @@
         <v>3</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -820,7 +820,7 @@
         <v>2</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -837,7 +837,7 @@
         <v>2</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -854,7 +854,7 @@
         <v>2</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -868,10 +868,10 @@
         <v>1003</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -888,7 +888,7 @@
         <v>3</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/SpawnRoots.xlsx
+++ b/Assets/Configs/SpawnRoots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506FDCCF-35F6-4CB5-AB24-90F1AFC6C7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16A8CCC-84AE-4BE2-94C1-48B0B269CDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,7 +358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="5" width="12.796875" customWidth="1"/>
@@ -548,24 +548,24 @@
         <v>3</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D12">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -573,7 +573,7 @@
         <v>102</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>1002</v>
@@ -590,16 +590,16 @@
         <v>102</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
         <v>1002</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -607,7 +607,7 @@
         <v>102</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15">
         <v>1002</v>
@@ -624,7 +624,7 @@
         <v>102</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16">
         <v>1002</v>
@@ -641,16 +641,16 @@
         <v>102</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>1002</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -658,7 +658,7 @@
         <v>102</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>1002</v>
@@ -675,7 +675,7 @@
         <v>102</v>
       </c>
       <c r="B19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19">
         <v>1002</v>
@@ -692,7 +692,7 @@
         <v>102</v>
       </c>
       <c r="B20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20">
         <v>1002</v>
@@ -701,7 +701,7 @@
         <v>2</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -709,50 +709,50 @@
         <v>102</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21">
         <v>1002</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C22">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D22">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C23">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D23">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -760,13 +760,13 @@
         <v>103</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24">
         <v>1003</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -777,13 +777,13 @@
         <v>103</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C25">
         <v>1003</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -794,7 +794,7 @@
         <v>103</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C26">
         <v>1003</v>
@@ -811,16 +811,16 @@
         <v>103</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>1003</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -828,16 +828,16 @@
         <v>103</v>
       </c>
       <c r="B28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28">
         <v>1003</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -845,7 +845,7 @@
         <v>103</v>
       </c>
       <c r="B29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>1003</v>
@@ -862,7 +862,7 @@
         <v>103</v>
       </c>
       <c r="B30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C30">
         <v>1003</v>
@@ -871,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -879,16 +879,67 @@
         <v>103</v>
       </c>
       <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31">
+        <v>1003</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>103</v>
+      </c>
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32">
+        <v>1003</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>103</v>
+      </c>
+      <c r="B33">
         <v>10</v>
       </c>
-      <c r="C31">
-        <v>1003</v>
-      </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-      <c r="E31">
-        <v>6</v>
+      <c r="C33">
+        <v>1003</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>103</v>
+      </c>
+      <c r="B34">
+        <v>11</v>
+      </c>
+      <c r="C34">
+        <v>1003</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/SpawnRoots.xlsx
+++ b/Assets/Configs/SpawnRoots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16A8CCC-84AE-4BE2-94C1-48B0B269CDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE73C3BF-5998-4FEA-BD1B-02D39DB87917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -359,9 +359,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="5" width="12.796875" customWidth="1"/>
+    <col min="1" max="5" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,7 +412,7 @@
         <v>0.6</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -426,10 +426,10 @@
         <v>1001</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -446,7 +446,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -463,7 +463,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -531,7 +531,7 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -548,7 +548,7 @@
         <v>3</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -565,7 +565,7 @@
         <v>4</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -582,7 +582,7 @@
         <v>0.6</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -599,7 +599,7 @@
         <v>0.6</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -633,7 +633,7 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -718,7 +718,7 @@
         <v>2</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -735,7 +735,7 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -752,7 +752,7 @@
         <v>3</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -769,7 +769,7 @@
         <v>0.6</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -786,7 +786,7 @@
         <v>0.6</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -803,7 +803,7 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -820,7 +820,7 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -854,7 +854,7 @@
         <v>2</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -871,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -905,7 +905,7 @@
         <v>2</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -922,7 +922,7 @@
         <v>3</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:5">

--- a/Assets/Configs/SpawnRoots.xlsx
+++ b/Assets/Configs/SpawnRoots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE73C3BF-5998-4FEA-BD1B-02D39DB87917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CAD8E4-DC2E-4260-8C51-B6941E2BBA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -359,9 +359,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="5" width="12.77734375" customWidth="1"/>
+    <col min="1" max="5" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,7 +412,7 @@
         <v>0.6</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -429,7 +429,7 @@
         <v>0.6</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -480,7 +480,7 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -647,7 +647,7 @@
         <v>1002</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -667,7 +667,7 @@
         <v>2</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -681,7 +681,7 @@
         <v>1002</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>1002</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -922,7 +922,7 @@
         <v>3</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -939,7 +939,7 @@
         <v>3</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
